--- a/isolated_excel/S&P 500 Total Return - Current.xlsx
+++ b/isolated_excel/S&P 500 Total Return - Current.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Source and Method'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4402,8 +4402,42 @@
         <v>-0.06349317981017011</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>16763.419921875</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>17219.939453125</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0.0272330785351429</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>2.72330785351429</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H116"/>
+  <autoFilter ref="A1:H117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4453,7 +4487,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
+          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/S&P 500 Total Return - Current.xlsx
+++ b/isolated_excel/S&P 500 Total Return - Current.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Source and Method'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4436,8 +4436,42 @@
         <v>2.72330785351429</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Sept 2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>17219.939453125</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>17160.41015625</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>-0.003456998036319825</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>-0.3456998036319825</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H117"/>
+  <autoFilter ref="A1:H118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4487,7 +4521,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
+          <t>Jan 2017 to Sept 2026; 117 monthly observations</t>
         </is>
       </c>
     </row>
